--- a/food_prices.xlsx
+++ b/food_prices.xlsx
@@ -8,19 +8,62 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meihan055\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B37E3E-D324-4495-971E-B7C2BC80DD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D40B579-D826-4CE0-A3E9-73D9C364E023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="食材価格" sheetId="1" r:id="rId1"/>
+    <sheet name="週次設定" sheetId="1" r:id="rId1"/>
+    <sheet name="食材価格" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>期間開始日</t>
+  </si>
+  <si>
+    <t>2026/4/24</t>
+  </si>
+  <si>
+    <t>期間終了日</t>
+  </si>
+  <si>
+    <t>2026/4/30</t>
+  </si>
+  <si>
+    <t>東京玉子基準値</t>
+  </si>
+  <si>
+    <t>東京前週比</t>
+  </si>
+  <si>
+    <t>大阪玉子基準値</t>
+  </si>
+  <si>
+    <t>大阪前週比</t>
+  </si>
+  <si>
+    <t>名古屋玉子基準値</t>
+  </si>
+  <si>
+    <t>名古屋前週比</t>
+  </si>
+  <si>
+    <t>玉子市況</t>
+  </si>
+  <si>
+    <t>玉子発表日</t>
+  </si>
   <si>
     <t>カテゴリ</t>
   </si>
@@ -119,13 +162,17 @@
   </si>
   <si>
     <t>円/L</t>
+  </si>
+  <si>
+    <t>強含み(やや上昇基調)</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,13 +195,27 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -175,9 +236,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -186,7 +250,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{AA8B2750-FD2F-42DB-98E2-349664C87F05}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -484,6 +548,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
@@ -495,27 +662,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>300</v>
@@ -524,15 +691,15 @@
         <v>315</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>118</v>
@@ -541,15 +708,15 @@
         <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>105</v>
@@ -558,15 +725,15 @@
         <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>108</v>
@@ -575,15 +742,15 @@
         <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>115</v>
@@ -592,15 +759,15 @@
         <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>110</v>
@@ -609,15 +776,15 @@
         <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>120</v>
@@ -626,15 +793,15 @@
         <v>145</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>118</v>
@@ -643,15 +810,15 @@
         <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>112</v>
@@ -660,15 +827,15 @@
         <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>95</v>
@@ -677,15 +844,15 @@
         <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>105</v>
@@ -694,15 +861,15 @@
         <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>130</v>
@@ -711,15 +878,15 @@
         <v>160</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>115</v>
@@ -728,15 +895,15 @@
         <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>680</v>
@@ -745,15 +912,15 @@
         <v>720</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>890</v>
@@ -762,15 +929,15 @@
         <v>920</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>1850</v>
@@ -779,15 +946,15 @@
         <v>1920</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>95</v>
@@ -796,15 +963,15 @@
         <v>98</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <v>380</v>
@@ -813,7 +980,7 @@
         <v>410</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/food_prices.xlsx
+++ b/food_prices.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="週次設定" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,67 +12,32 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="履歴" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <sz val="6"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -92,24 +58,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0"/>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -471,19 +429,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>値</t>
         </is>
@@ -529,8 +487,10 @@
           <t>東京前週比</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>5</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -549,8 +509,10 @@
           <t>大阪前週比</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>5</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -569,8 +531,10 @@
           <t>名古屋前週比</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -581,7 +545,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>強含み(やや上昇基調)</t>
+          <t>保合（小幅変動横ばい）</t>
         </is>
       </c>
     </row>
@@ -609,11 +573,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="4"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -797,7 +762,7 @@
         <v>120</v>
       </c>
       <c r="D8" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -912,7 +877,7 @@
         <v>130</v>
       </c>
       <c r="D13" t="n">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1069,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1086,110 +1051,59 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>期間開始日</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>期間終了日</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>東京基準値</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>東京前週比</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>大阪基準値</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>大阪前週比</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>名古屋基準値</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>名古屋前週比</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>玉子市況</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>報告書ファイル名</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>実行日時</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026/4/24</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026/4/30</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>315</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>315</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>315</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>強含み(やや上昇基調)</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>週次報告書_20260430_152310.docx</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026/04/30 15:23</t>
         </is>
       </c>
     </row>
